--- a/Config/Datas/Tables/j_角色_CharacterConfig.xlsx
+++ b/Config/Datas/Tables/j_角色_CharacterConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbCharacter" sheetId="1" r:id="Rf80a140955b042a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbCharacter" sheetId="1" r:id="R935e52e78556435c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2123,6 +2123,112 @@
       <x:c r="Q34"/>
       <x:c r="R34"/>
     </x:row>
+    <x:row r="35">
+      <x:c r="B35" t="n">
+        <x:v>10101</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>磐岳</x:v>
+      </x:c>
+      <x:c r="D35" t="n">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="E35" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F35" t="n">
+        <x:v>20043</x:v>
+      </x:c>
+      <x:c r="G35" t="n">
+        <x:v>30.815</x:v>
+      </x:c>
+      <x:c r="H35" t="n">
+        <x:v>30.815</x:v>
+      </x:c>
+      <x:c r="I35" t="n">
+        <x:v>146.522</x:v>
+      </x:c>
+      <x:c r="J35" t="n">
+        <x:v>0.485</x:v>
+      </x:c>
+      <x:c r="K35" t="n">
+        <x:v>72.66</x:v>
+      </x:c>
+      <x:c r="L35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M35" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="N35" t="n">
+        <x:v>0.485</x:v>
+      </x:c>
+      <x:c r="O35" t="n">
+        <x:v>72.66</x:v>
+      </x:c>
+      <x:c r="P35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q35" t="n">
+        <x:v>0.485</x:v>
+      </x:c>
+      <x:c r="R35" t="n">
+        <x:v>72.66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="B36" t="n">
+        <x:v>10201</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>周天</x:v>
+      </x:c>
+      <x:c r="D36" t="n">
+        <x:v>10022</x:v>
+      </x:c>
+      <x:c r="E36" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F36" t="n">
+        <x:v>20033</x:v>
+      </x:c>
+      <x:c r="G36" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H36" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I36" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J36" t="n">
+        <x:v>-10.7</x:v>
+      </x:c>
+      <x:c r="K36" t="n">
+        <x:v>56.8</x:v>
+      </x:c>
+      <x:c r="L36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M36" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="N36" t="n">
+        <x:v>-10.7</x:v>
+      </x:c>
+      <x:c r="O36" t="n">
+        <x:v>56.8</x:v>
+      </x:c>
+      <x:c r="P36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
